--- a/data/Efectos_electronica_y_electricidad.xlsx
+++ b/data/Efectos_electronica_y_electricidad.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/12ef92c0183a0afd/IA/trabajo final de IA/Datos modificados para el proyeto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Proyectos_Personales\Sistema_Prediccion_Repuestos_Insumos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_6F0489211DDC1A106A8D54489204EDC99F8FA4B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF805F8B-06B3-4F4E-AE6C-DCE8CDA3D979}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD2167D-6339-470E-B9C4-7CC6B01A6028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-7650" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>N° Ord</t>
   </si>
@@ -262,6 +262,12 @@
   </si>
   <si>
     <t>EQUIPO DE RADIO.MOD</t>
+  </si>
+  <si>
+    <t>E00039</t>
+  </si>
+  <si>
+    <t>NO CATALOGADO</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1119,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -1554,6 +1560,17 @@
       </c>
       <c r="C40" s="7" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
